--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="559">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:41:23+00:00</t>
+    <t>2026-09-15T14:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system= $loinc ).exists() or coding.where(system= $sct ).exists() or coding.where(system= $dgai).exists() or coding.where(system= $ieee-11073).exists()}mii-icu-comp-xor-val:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() xor value.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icu-comp-xor-val:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() xor value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -827,6 +827,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system='http://loinc.org').exists() or coding.where(system='http://snomed.info/sct').exists() or coding.where(system='urn:iso:std:iso:11073:10101').exists() or coding.where(system='http://dgai.de').exists()}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -5283,30 +5287,30 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>261</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5418,10 +5422,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5535,10 +5539,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5546,7 +5550,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>80</v>
@@ -5652,13 +5656,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>81</v>
@@ -5702,7 +5706,7 @@
         <v>81</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>81</v>
@@ -5721,7 +5725,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5771,10 +5775,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5886,10 +5890,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6003,10 +6007,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6051,7 +6055,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -6122,10 +6126,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6239,10 +6243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6356,10 +6360,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6473,10 +6477,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6592,13 +6596,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>81</v>
@@ -6642,7 +6646,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6661,7 +6665,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6711,10 +6715,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6826,10 +6830,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6943,10 +6947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6991,7 +6995,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -7062,10 +7066,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7179,10 +7183,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7296,10 +7300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7413,10 +7417,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7532,13 +7536,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>81</v>
@@ -7582,7 +7586,7 @@
         <v>81</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>81</v>
@@ -7601,7 +7605,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7651,10 +7655,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7766,10 +7770,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7883,10 +7887,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7931,7 +7935,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -8002,10 +8006,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8119,10 +8123,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8236,10 +8240,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8353,10 +8357,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8472,10 +8476,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8591,10 +8595,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8617,19 +8621,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8678,7 +8682,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8693,16 +8697,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8710,10 +8714,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8736,16 +8740,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8795,7 +8799,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8816,10 +8820,10 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8827,14 +8831,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8853,19 +8857,19 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8914,7 +8918,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8929,16 +8933,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8946,14 +8950,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8972,19 +8976,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9033,7 +9037,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9048,16 +9052,16 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9065,10 +9069,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9091,16 +9095,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9150,7 +9154,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9171,10 +9175,10 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9182,10 +9186,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9208,17 +9212,17 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9267,7 +9271,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9282,16 +9286,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -9299,10 +9303,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9325,19 +9329,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9347,7 +9351,7 @@
         <v>81</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>81</v>
@@ -9386,7 +9390,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9395,7 +9399,7 @@
         <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>103</v>
@@ -9404,24 +9408,24 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9533,10 +9537,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9650,10 +9654,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9676,19 +9680,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9737,7 +9741,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9758,7 +9762,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9769,10 +9773,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9798,20 +9802,20 @@
         <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>81</v>
@@ -9835,10 +9839,10 @@
         <v>175</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9856,7 +9860,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9877,7 +9881,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9888,10 +9892,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9917,14 +9921,14 @@
         <v>193</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9973,7 +9977,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9994,7 +9998,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10005,10 +10009,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10034,14 +10038,14 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10051,7 +10055,7 @@
         <v>81</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>81</v>
@@ -10090,7 +10094,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10099,7 +10103,7 @@
         <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
@@ -10111,7 +10115,7 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10122,10 +10126,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10151,16 +10155,16 @@
         <v>111</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10209,7 +10213,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10230,7 +10234,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10241,10 +10245,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10270,16 +10274,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10304,13 +10308,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -10328,7 +10332,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10337,7 +10341,7 @@
         <v>91</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>103</v>
@@ -10349,7 +10353,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10360,14 +10364,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10389,16 +10393,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10423,13 +10427,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10447,7 +10451,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10465,24 +10469,24 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10505,19 +10509,19 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10566,7 +10570,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10587,7 +10591,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10598,10 +10602,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10627,13 +10631,13 @@
         <v>183</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10659,11 +10663,11 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -10681,7 +10685,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10699,24 +10703,24 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10742,16 +10746,16 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10779,10 +10783,10 @@
         <v>258</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10800,7 +10804,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10821,7 +10825,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -10832,10 +10836,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10858,16 +10862,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10917,7 +10921,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10935,24 +10939,24 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10975,16 +10979,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11034,7 +11038,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11052,24 +11056,24 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11092,19 +11096,19 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11153,7 +11157,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11165,7 +11169,7 @@
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>81</v>
@@ -11174,7 +11178,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11185,10 +11189,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11300,10 +11304,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11417,14 +11421,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11446,10 +11450,10 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>138</v>
@@ -11504,7 +11508,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11536,10 +11540,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11562,13 +11566,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11619,7 +11623,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11628,7 +11632,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11640,7 +11644,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -11651,10 +11655,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11677,13 +11681,13 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11734,7 +11738,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11743,7 +11747,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11755,7 +11759,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -11766,10 +11770,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11795,16 +11799,16 @@
         <v>183</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11832,10 +11836,10 @@
         <v>115</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -11853,7 +11857,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11871,10 +11875,10 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -11885,10 +11889,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11914,16 +11918,16 @@
         <v>183</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11951,10 +11955,10 @@
         <v>258</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11972,7 +11976,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11990,10 +11994,10 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -12004,10 +12008,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12030,17 +12034,17 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12089,7 +12093,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12121,10 +12125,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12150,10 +12154,10 @@
         <v>193</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12204,7 +12208,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12225,7 +12229,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12236,10 +12240,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12262,16 +12266,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12321,7 +12325,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12342,7 +12346,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12353,10 +12357,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12379,16 +12383,16 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12438,7 +12442,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12459,7 +12463,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -12470,10 +12474,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12496,19 +12500,19 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12557,7 +12561,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12578,7 +12582,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12589,10 +12593,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12704,10 +12708,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12821,14 +12825,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12850,10 +12854,10 @@
         <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>138</v>
@@ -12908,7 +12912,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12940,10 +12944,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12969,13 +12973,13 @@
         <v>183</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>257</v>
@@ -13027,7 +13031,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>91</v>
@@ -13045,13 +13049,13 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13059,10 +13063,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13085,19 +13089,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13146,7 +13150,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13164,24 +13168,24 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13207,16 +13211,16 @@
         <v>183</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13241,13 +13245,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13265,7 +13269,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13274,7 +13278,7 @@
         <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>103</v>
@@ -13286,7 +13290,7 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
@@ -13297,14 +13301,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13326,16 +13330,16 @@
         <v>183</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13360,13 +13364,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13384,7 +13388,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13402,24 +13406,24 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13445,16 +13449,16 @@
         <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13503,7 +13507,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13524,7 +13528,7 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:01:05+00:00</t>
+    <t>2026-09-15T17:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T17:45:52+00:00</t>
+    <t>2026-09-15T20:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T20:38:45+00:00</t>
+    <t>2026-09-16T05:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:15:10+00:00</t>
+    <t>2026-09-16T08:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:10:08+00:00</t>
+    <t>2026-09-17T08:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T08:26:08+00:00</t>
+    <t>2026-09-17T12:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-vent-mittlerer-beatmungsdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:53:08+00:00</t>
+    <t>2026-09-23T08:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
